--- a/data/trans_orig/IQ28_P-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición</t>
+          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +677,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,01; 37,74</t>
+          <t>29,89; 37,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,05; 36,3</t>
+          <t>28,97; 36,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,71; 38,15</t>
+          <t>27,49; 38,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,38; 37,85</t>
+          <t>30,52; 37,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 42,14</t>
+          <t>32,05; 41,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,61; 39,45</t>
+          <t>29,27; 40,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,23; 36,29</t>
+          <t>31,42; 36,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,48; 37,82</t>
+          <t>31,77; 38,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,74; 37,09</t>
+          <t>29,9; 37,25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +787,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,33; 35,95</t>
+          <t>30,07; 35,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,72; 38,48</t>
+          <t>32,97; 38,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,72; 57,17</t>
+          <t>35,77; 56,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,68; 35,34</t>
+          <t>30,78; 35,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,27; 36,14</t>
+          <t>31,38; 36,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,48; 49,72</t>
+          <t>33,74; 50,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,07; 34,75</t>
+          <t>31,36; 34,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,82; 36,45</t>
+          <t>32,72; 36,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,3; 53,18</t>
+          <t>37,14; 53,3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,28; 36,37</t>
+          <t>29,37; 36,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,48; 38,06</t>
+          <t>31,02; 37,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,16; 45,13</t>
+          <t>33,77; 45,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,0; 43,24</t>
+          <t>34,89; 42,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,99; 37,9</t>
+          <t>31,1; 37,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,32; 46,82</t>
+          <t>35,29; 46,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,82; 38,34</t>
+          <t>32,71; 38,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,12; 36,81</t>
+          <t>32,18; 36,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,35; 43,83</t>
+          <t>35,83; 44,17</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,37; 36,76</t>
+          <t>30,61; 36,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,78; 43,19</t>
+          <t>34,7; 43,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,05; 50,17</t>
+          <t>34,52; 49,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,78; 38,12</t>
+          <t>31,17; 38,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,68; 44,92</t>
+          <t>35,94; 45,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,38; 43,55</t>
+          <t>29,81; 43,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,42; 36,46</t>
+          <t>31,46; 36,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,44; 42,76</t>
+          <t>36,42; 42,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,09; 43,82</t>
+          <t>33,61; 44,07</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1117,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,52; 36,77</t>
+          <t>28,5; 36,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,48; 35,67</t>
+          <t>28,71; 35,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,78; 38,58</t>
+          <t>29,53; 39,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,48; 43,03</t>
+          <t>32,66; 43,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,57; 40,39</t>
+          <t>32,54; 40,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,6; 52,33</t>
+          <t>37,29; 53,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,5; 38,79</t>
+          <t>31,61; 39,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,5; 36,82</t>
+          <t>31,48; 36,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,35; 44,59</t>
+          <t>35,54; 45,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1227,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,49; 41,52</t>
+          <t>33,71; 41,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,87; 39,58</t>
+          <t>33,15; 40,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,72; 41,02</t>
+          <t>31,42; 41,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,26; 43,37</t>
+          <t>34,44; 43,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,93; 41,48</t>
+          <t>33,62; 41,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,92; 48,35</t>
+          <t>34,84; 47,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,94; 41,05</t>
+          <t>35,19; 41,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,15; 39,43</t>
+          <t>34,5; 39,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,88; 43,12</t>
+          <t>34,79; 43,87</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,07; 38,76</t>
+          <t>33,06; 38,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,09; 35,34</t>
+          <t>31,11; 35,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,45; 44,3</t>
+          <t>34,1; 44,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32,64; 38,42</t>
+          <t>32,74; 38,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,18; 35,89</t>
+          <t>31,12; 35,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,93; 46,85</t>
+          <t>38,13; 47,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,69; 37,51</t>
+          <t>33,56; 37,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,79; 35,07</t>
+          <t>31,93; 35,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,45; 44,67</t>
+          <t>37,85; 44,61</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,15; 36,18</t>
+          <t>32,1; 36,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,62; 35,44</t>
+          <t>31,48; 35,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,14; 38,62</t>
+          <t>32,84; 38,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,12; 37,46</t>
+          <t>33,54; 37,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,71; 36,07</t>
+          <t>31,45; 36,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,86; 45,94</t>
+          <t>38,8; 45,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,24; 36,1</t>
+          <t>33,34; 36,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,1; 35,05</t>
+          <t>32,21; 35,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37,16; 42,35</t>
+          <t>37,24; 42,4</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33,02; 35,16</t>
+          <t>33,07; 35,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33,25; 35,31</t>
+          <t>33,28; 35,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,17; 46,03</t>
+          <t>36,26; 45,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34,33; 36,62</t>
+          <t>34,34; 36,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,02</t>
+          <t>33,95; 36,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,76; 42,84</t>
+          <t>38,64; 42,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,0; 35,5</t>
+          <t>34,05; 35,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33,94; 35,45</t>
+          <t>33,88; 35,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,19; 43,09</t>
+          <t>38,18; 43,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
+          <t>Peso medio, en kilogramos, recogido por medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,89; 37,73</t>
+          <t>29,83; 37,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,97; 36,31</t>
+          <t>29,16; 36,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,49; 38,26</t>
+          <t>27,58; 37,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,52; 37,77</t>
+          <t>30,78; 38,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,05; 41,89</t>
+          <t>31,63; 41,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,27; 40,05</t>
+          <t>29,3; 40,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,42; 36,51</t>
+          <t>31,33; 36,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,77; 38,14</t>
+          <t>31,92; 38,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,9; 37,25</t>
+          <t>30,1; 37,5</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,07; 35,33</t>
+          <t>30,28; 35,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,97; 38,35</t>
+          <t>32,59; 38,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,77; 56,93</t>
+          <t>34,82; 56,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,78; 35,54</t>
+          <t>30,55; 35,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,38; 36,19</t>
+          <t>31,38; 36,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,74; 50,33</t>
+          <t>34,44; 50,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,36; 34,74</t>
+          <t>31,24; 34,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,72; 36,38</t>
+          <t>32,67; 36,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,14; 53,3</t>
+          <t>37,02; 53,65</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,37; 36,16</t>
+          <t>29,51; 36,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,02; 37,74</t>
+          <t>31,44; 37,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,77; 45,19</t>
+          <t>33,98; 45,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,89; 42,92</t>
+          <t>34,81; 42,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,1; 37,69</t>
+          <t>30,99; 38,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,29; 46,56</t>
+          <t>35,5; 46,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,71; 38,31</t>
+          <t>32,7; 38,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,18; 36,96</t>
+          <t>31,98; 36,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,83; 44,17</t>
+          <t>36,47; 44,54</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,61; 36,82</t>
+          <t>30,47; 36,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,7; 43,77</t>
+          <t>34,5; 42,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,52; 49,98</t>
+          <t>34,31; 49,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,17; 38,39</t>
+          <t>31,06; 38,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,94; 45,23</t>
+          <t>35,73; 44,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,81; 43,51</t>
+          <t>29,48; 43,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,46; 36,23</t>
+          <t>31,62; 36,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,42; 42,8</t>
+          <t>36,04; 42,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,61; 44,07</t>
+          <t>33,64; 44,34</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,5; 36,63</t>
+          <t>28,36; 37,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,71; 35,66</t>
+          <t>28,55; 35,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,53; 39,25</t>
+          <t>29,56; 39,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,66; 43,69</t>
+          <t>32,01; 42,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,54; 40,56</t>
+          <t>32,72; 40,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,29; 53,42</t>
+          <t>37,84; 53,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,61; 39,01</t>
+          <t>31,42; 38,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,48; 36,93</t>
+          <t>31,28; 36,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,54; 45,65</t>
+          <t>35,5; 45,43</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,71; 41,47</t>
+          <t>33,81; 41,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,15; 40,1</t>
+          <t>32,75; 39,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,42; 41,7</t>
+          <t>31,44; 41,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,44; 43,62</t>
+          <t>34,33; 43,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,62; 41,63</t>
+          <t>33,46; 41,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,84; 47,67</t>
+          <t>34,55; 46,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,19; 41,2</t>
+          <t>35,14; 41,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,5; 39,54</t>
+          <t>34,23; 39,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,79; 43,87</t>
+          <t>34,86; 43,88</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,06; 38,27</t>
+          <t>32,74; 38,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,11; 35,4</t>
+          <t>30,95; 35,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,1; 44,0</t>
+          <t>34,13; 44,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32,74; 38,31</t>
+          <t>32,89; 38,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,12; 35,93</t>
+          <t>31,14; 36,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,13; 47,07</t>
+          <t>38,03; 47,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,56; 37,51</t>
+          <t>33,66; 37,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,93; 35,06</t>
+          <t>31,81; 35,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,85; 44,61</t>
+          <t>37,74; 44,52</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,1; 36,0</t>
+          <t>32,17; 36,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,48; 35,41</t>
+          <t>31,53; 35,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,84; 38,37</t>
+          <t>33,05; 38,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,54; 37,51</t>
+          <t>33,47; 37,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,45; 36,16</t>
+          <t>31,73; 35,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,8; 45,88</t>
+          <t>38,8; 45,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,34; 36,18</t>
+          <t>33,3; 36,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,21; 35,09</t>
+          <t>32,12; 34,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37,24; 42,4</t>
+          <t>37,29; 42,24</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33,07; 35,17</t>
+          <t>32,85; 35,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33,28; 35,26</t>
+          <t>33,24; 35,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,26; 45,96</t>
+          <t>36,26; 46,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34,34; 36,69</t>
+          <t>34,36; 36,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,95; 36,18</t>
+          <t>33,86; 36,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,64; 42,94</t>
+          <t>38,81; 42,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,05; 35,59</t>
+          <t>34,06; 35,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33,88; 35,38</t>
+          <t>33,9; 35,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,18; 43,06</t>
+          <t>38,35; 43,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Provincia-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33,97</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36,27</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35,54</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>33,72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>32,43</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32,32</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33,97</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,27</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,16</t>
+          <t>31,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,36</t>
+          <t>33,74</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,83; 37,63</t>
+          <t>30,38; 37,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,16; 36,4</t>
+          <t>32,23; 42,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,58; 37,85</t>
+          <t>30,6; 40,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,78; 38,63</t>
+          <t>30,01; 37,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,63; 41,85</t>
+          <t>29,05; 36,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,3; 40,1</t>
+          <t>27,64; 37,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,33; 36,84</t>
+          <t>31,23; 36,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,92; 38,16</t>
+          <t>31,48; 37,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,5</t>
+          <t>30,41; 37,4</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32,88</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33,59</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40,98</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>32,67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>35,46</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>47,44</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32,88</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,59</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,58</t>
+          <t>38,71</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44,53</t>
+          <t>39,91</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,28; 35,61</t>
+          <t>30,68; 35,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,59; 38,18</t>
+          <t>31,27; 36,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,82; 56,57</t>
+          <t>35,07; 49,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,55; 35,1</t>
+          <t>30,33; 35,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,38; 36,25</t>
+          <t>32,72; 38,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,44; 50,48</t>
+          <t>33,81; 44,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,24; 34,78</t>
+          <t>31,07; 34,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,67; 36,43</t>
+          <t>32,82; 36,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,02; 53,65</t>
+          <t>35,81; 46,01</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>38,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,26</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41,51</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>32,58</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>34,62</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38,6</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34,26</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,92</t>
+          <t>39,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40,09</t>
+          <t>40,42</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,51; 36,73</t>
+          <t>35,0; 43,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,44; 37,89</t>
+          <t>30,99; 37,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,98; 45,45</t>
+          <t>36,53; 47,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,81; 42,92</t>
+          <t>29,28; 36,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,99; 38,16</t>
+          <t>31,48; 38,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,5; 46,79</t>
+          <t>34,32; 44,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,7; 38,3</t>
+          <t>32,82; 38,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,98; 36,92</t>
+          <t>32,12; 36,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,47; 44,54</t>
+          <t>36,83; 43,96</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34,19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40,23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>36,7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>33,5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>38,61</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40,92</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,23</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,85</t>
+          <t>41,44</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38,47</t>
+          <t>39,26</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,47; 36,91</t>
+          <t>30,78; 38,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,5; 42,85</t>
+          <t>35,68; 44,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,31; 49,65</t>
+          <t>31,6; 44,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,06; 38,34</t>
+          <t>30,37; 36,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,73; 44,73</t>
+          <t>34,78; 43,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,48; 43,3</t>
+          <t>34,48; 51,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,62; 36,47</t>
+          <t>31,42; 36,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,04; 42,51</t>
+          <t>36,44; 42,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,64; 44,34</t>
+          <t>34,99; 45,14</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>37,45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36,21</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>44,09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>32,42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>31,67</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37,45</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>36,21</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,5</t>
+          <t>34,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39,14</t>
+          <t>39,56</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,36; 37,05</t>
+          <t>32,48; 43,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,55; 35,69</t>
+          <t>32,57; 40,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,56; 39,51</t>
+          <t>38,24; 53,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,01; 42,69</t>
+          <t>28,52; 36,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 40,04</t>
+          <t>28,48; 35,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,84; 53,46</t>
+          <t>30,11; 39,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,42; 38,92</t>
+          <t>31,5; 38,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,28; 36,46</t>
+          <t>31,5; 36,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,5; 45,43</t>
+          <t>35,8; 44,91</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38,73</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37,36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40,91</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>37,33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>36,27</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36,37</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38,73</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>37,36</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,62</t>
+          <t>36,83</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38,98</t>
+          <t>39,21</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,81; 41,47</t>
+          <t>34,26; 43,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,75; 39,61</t>
+          <t>33,93; 41,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,44; 41,25</t>
+          <t>35,15; 48,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,33; 43,57</t>
+          <t>33,49; 41,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,46; 41,11</t>
+          <t>32,87; 39,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,55; 46,73</t>
+          <t>32,15; 41,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,14; 41,03</t>
+          <t>34,94; 41,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,23; 39,34</t>
+          <t>34,15; 39,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,86; 43,88</t>
+          <t>35,26; 43,31</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35,43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33,56</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43,08</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>35,64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>33,21</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35,43</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,56</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,14</t>
+          <t>40,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40,9</t>
+          <t>42,11</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,74; 38,52</t>
+          <t>32,64; 38,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,95; 35,16</t>
+          <t>31,18; 35,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,13; 44,13</t>
+          <t>38,94; 48,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32,89; 38,6</t>
+          <t>33,07; 38,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,14; 36,36</t>
+          <t>31,09; 35,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,03; 47,37</t>
+          <t>36,71; 45,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,66; 37,64</t>
+          <t>33,69; 37,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,81; 35,07</t>
+          <t>31,79; 35,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,74; 44,52</t>
+          <t>38,76; 45,55</t>
         </is>
       </c>
     </row>
@@ -1394,32 +1394,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35,34</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33,74</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>42,9</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>33,99</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>33,38</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>35,77</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>35,34</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>33,74</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,23</t>
+          <t>36,62</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39,6</t>
+          <t>40,32</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,17; 36,03</t>
+          <t>33,12; 37,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,53; 35,42</t>
+          <t>31,71; 36,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,05; 38,48</t>
+          <t>39,54; 46,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,47; 37,69</t>
+          <t>32,15; 36,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,73; 35,99</t>
+          <t>31,62; 35,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,8; 45,9</t>
+          <t>33,97; 39,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,3; 36,08</t>
+          <t>33,24; 36,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,12; 34,96</t>
+          <t>32,1; 35,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37,29; 42,24</t>
+          <t>37,8; 43,01</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>35,45</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>34,98</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>41,57</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>34,06</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>34,29</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>39,24</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>35,45</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>34,98</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,67</t>
+          <t>37,67</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40,02</t>
+          <t>39,83</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32,85; 35,06</t>
+          <t>34,33; 36,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33,24; 35,3</t>
+          <t>33,92; 36,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,26; 46,47</t>
+          <t>39,65; 43,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34,36; 36,64</t>
+          <t>33,02; 35,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,86; 36,12</t>
+          <t>33,25; 35,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,81; 42,98</t>
+          <t>35,93; 39,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,06; 35,59</t>
+          <t>34,0; 35,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33,9; 35,41</t>
+          <t>33,94; 35,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,35; 43,54</t>
+          <t>38,44; 41,2</t>
         </is>
       </c>
     </row>
